--- a/src/attributions/attributions_ig_traj_444.xlsx
+++ b/src/attributions/attributions_ig_traj_444.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1119557869065137</v>
+        <v>0.03063931049689601</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.006269620104170185</v>
+        <v>-0.01221863705520963</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02435258306680509</v>
+        <v>-0.007043323351652384</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1564069789428789</v>
+        <v>0.08791048667019601</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.009353178166846856</v>
+        <v>-0.042902961030631</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1050,67 +1050,67 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.09237955110702602</v>
+        <v>-0.0152782161746577</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09173261371066502</v>
+        <v>0.01438419024337583</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.05591904119654142</v>
+        <v>-0.02837158220421699</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001579407849506565</v>
+        <v>-0.002647466714541359</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03172387293051325</v>
+        <v>-0.01264217565598267</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.03206557820914779</v>
+        <v>-0.01543098693672483</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.002287583687579504</v>
+        <v>0.006380345058300312</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05745207443040867</v>
+        <v>0.02221064197700664</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,34 +1119,34 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.005924793711966913</v>
+        <v>-0.002873378803451356</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.03222569949416512</v>
+        <v>-0.001302664603507355</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.342257218442478</v>
+        <v>0.1332090899478599</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1946694666514021</v>
+        <v>-0.03127320006779764</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.05871188157103844</v>
+        <v>-0.0004140977164185829</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.009692833802689451</v>
+        <v>-0.01164435688451584</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.05899650778167679</v>
+        <v>-0.01896279215780035</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,16 +1182,16 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.07140179558843039</v>
+        <v>-0.02293848143626346</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.04121006165406185</v>
+        <v>0.01856272326405501</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
@@ -1200,34 +1200,34 @@
         <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1686239715384837</v>
+        <v>0.0540387394015916</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.04287443334894736</v>
+        <v>0.01931727492317938</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1820566462414447</v>
+        <v>0.06814546581197196</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.008136172867675465</v>
+        <v>-0.02619955329475364</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1236,124 +1236,124 @@
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.03544625352344381</v>
+        <v>-0.01444737985829482</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.07712118033990228</v>
+        <v>-0.03194426455061893</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.004081092570111233</v>
+        <v>0.01508650883799615</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.05046530107517962</v>
+        <v>0.01530054574044443</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.006579934298579931</v>
+        <v>-0.01595230449173424</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.02900688073700627</v>
+        <v>0.002787542529345154</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.000941203045526322</v>
+        <v>0.002957027506832138</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.08276630305223066</v>
+        <v>-0.03198125080208882</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.009091362285733717</v>
+        <v>0.009761381376438585</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.03099472632202777</v>
+        <v>0.01710708797103535</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.08021901117326097</v>
+        <v>-0.05986453363818223</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0478335670285695</v>
+        <v>2.932523973140822e-05</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.005926915582458726</v>
+        <v>0.002194987743124821</v>
       </c>
       <c r="DN2" t="n">
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.01299907193770447</v>
+        <v>-0.01287095423626931</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,37 +1362,37 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.04085434235240467</v>
+        <v>0.01571049938263521</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.0100251851565695</v>
+        <v>0.01490343198362009</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1382140107905027</v>
+        <v>-0.01867851356909968</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.03088703453364123</v>
+        <v>-0.01991794792700052</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,13 +1401,13 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.03993698109187577</v>
+        <v>-0.0008806925268618017</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.05649120904799688</v>
+        <v>-0.02488607301382933</v>
       </c>
       <c r="EH2" t="n">
         <v>-0</v>
@@ -1416,79 +1416,79 @@
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.01324109954035662</v>
+        <v>-0.004559516245565966</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.08730631932813814</v>
+        <v>0.01367910395037539</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.06231207059746063</v>
+        <v>-0.01018043657749745</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.01558004065351027</v>
+        <v>0.01379692133401073</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.06711783706092306</v>
+        <v>0.01598908127620979</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.08734004212493762</v>
+        <v>-0.04325117256387017</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.002860953820012634</v>
+        <v>0.008358735698066694</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.03220591333436644</v>
+        <v>0.01478540256445596</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.001178399468943418</v>
+        <v>0.03587028481439943</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,52 +1497,52 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.06256833486035958</v>
+        <v>-0.01579642113852405</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0.01364318111454316</v>
+        <v>0.02666608466857538</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01063175862691304</v>
+        <v>-0.008805626396265238</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.001854211006475435</v>
+        <v>0.00911935187050863</v>
       </c>
       <c r="FU2" t="n">
         <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.02383070272340733</v>
+        <v>0.002920476125652946</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.05229351848679406</v>
+        <v>-0.02141740779895676</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,19 +1551,19 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.07772608736088633</v>
+        <v>-0.01097510666498126</v>
       </c>
     </row>
     <row r="3">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2031242477094362</v>
+        <v>0.001525877997368635</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,16 +2718,16 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0263694166195829</v>
+        <v>0.0002404073531801195</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.07070870917589635</v>
+        <v>-0.0006586041756332898</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2198782285486201</v>
+        <v>0.004187188686304646</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,16 +2745,16 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04468542091333901</v>
+        <v>-9.678428314074467e-05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1201376426239863</v>
+        <v>-0.002148998015241074</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2763,115 +2763,115 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09319977076111503</v>
+        <v>0.0004013979754681614</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08575384898239925</v>
+        <v>-0.001781743304838477</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.02887256588496505</v>
+        <v>-0.0003261936530991924</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.06391925116257058</v>
+        <v>-0.0003398995772075948</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.008147709946504631</v>
+        <v>-0.0003874966724004128</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01011553963933936</v>
+        <v>-0.0002013139957998044</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.04620032771711633</v>
+        <v>0.0002865435948681958</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.04036146592873315</v>
+        <v>0.0006366019350192347</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.0591061215964155</v>
+        <v>-0.0002847343546177184</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3696114569106919</v>
+        <v>0.005594184431221146</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2043333725706908</v>
+        <v>7.904134271849443e-05</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.1835221163657897</v>
+        <v>-0.0005394681351747259</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.04028490824433388</v>
+        <v>-0.001011663009679825</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.08655272829080513</v>
+        <v>-0.0008114152428874785</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.003742794285311714</v>
+        <v>-0.0002882138050305954</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.04287663752206976</v>
+        <v>0.0009793964731679584</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0494352149351222</v>
+        <v>0.002532465060336218</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1036901924945408</v>
+        <v>-0.0005579671223622056</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,52 +2922,52 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1676391801862338</v>
+        <v>0.002405245897230358</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.07644888656666177</v>
+        <v>-4.801290404894963e-05</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.08336548051167846</v>
+        <v>-0.0002888289675884118</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.09173356777050247</v>
+        <v>-0.0009592472395606311</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02791078211976699</v>
+        <v>-8.65688263219307e-05</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0512390707325139</v>
+        <v>0.0005709043566248646</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
@@ -2979,49 +2979,49 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.006786898985079257</v>
+        <v>-0.0007998622060719941</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.0218468294087919</v>
+        <v>0.0001923593553325991</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.006264988338433519</v>
+        <v>-0.0002596659602901752</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.09309194887264384</v>
+        <v>-0.001040022298345592</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.04872951748594139</v>
+        <v>-0.0003441412676996658</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.06359540039761882</v>
+        <v>0.0007433123936527865</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.09328536299324547</v>
+        <v>-0.001729695730474567</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,40 +3042,40 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.04953603453872363</v>
+        <v>-0.002239225045919817</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.02478288452367555</v>
+        <v>0.0005430466499726836</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.009481483605645553</v>
+        <v>0.0002564521001814518</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.01798777526596903</v>
+        <v>-0.0004976501579130743</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.02462383482836847</v>
+        <v>0.001370225519251603</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
@@ -3084,28 +3084,28 @@
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.115132119306246</v>
+        <v>-0.001198195948737459</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.006269156882580773</v>
+        <v>-0.0008786564499695918</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.01589542512901682</v>
+        <v>0.001310451245504944</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,25 +3114,25 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0711763580756162</v>
+        <v>-0.0009083043861841247</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.003814026542092944</v>
+        <v>-0.0002807076792799499</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.06807198944751494</v>
+        <v>0.0002210729688513159</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,34 +3141,34 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0845497419461539</v>
+        <v>-0.0002846666571406405</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.1123588133441534</v>
+        <v>0.0001086869725495751</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.05339809223323486</v>
+        <v>0.0005752883988381173</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.09827080349572793</v>
+        <v>-0.001464625337755386</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,13 +3177,13 @@
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.05892744367984654</v>
+        <v>-0.000477129237181235</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.06528282513549338</v>
+        <v>0.0006018304036791595</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,64 +3192,64 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.007165364785449029</v>
+        <v>0.001184311047020221</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02342363256416062</v>
+        <v>-0.0003497146773082088</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.003494324961864666</v>
+        <v>-0.0006095459810381763</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01187518842025042</v>
+        <v>-0.0001011178222380029</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.0005678899250277649</v>
+        <v>0.0002869905264217018</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.06073783121705328</v>
+        <v>0.0007367981299907558</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
         <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.04909532501790893</v>
+        <v>-0.0009603564694198425</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3261,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>-0.03705001528004435</v>
+        <v>0.0005607612971694786</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4365102872371688</v>
+        <v>0.4720530952280757</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3611492832469658</v>
+        <v>-0.3448282305931418</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01135874265310389</v>
+        <v>-0.02670931815444035</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.452914743979049</v>
+        <v>0.66520101071875</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3697941711078131</v>
+        <v>-0.4429869475637067</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.09054716269225273</v>
+        <v>-0.1562876697867785</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1907727009361307</v>
+        <v>0.2884851221491319</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.043983623668901</v>
+        <v>-0.09458632593446423</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1470746024281799</v>
+        <v>-0.05797541343973109</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,28 +3925,28 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06421759750593643</v>
+        <v>-0.05126304873921964</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.00390028154312514</v>
+        <v>0.07457691152768114</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.001779309647612596</v>
+        <v>-0.06477202583813005</v>
       </c>
       <c r="AG7" t="n">
         <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -3955,43 +3955,43 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04083924112515695</v>
+        <v>0.2764479555039223</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.09710914511915773</v>
+        <v>-0.1433777472077767</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.07736631215413579</v>
+        <v>0.1820838609300645</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.6390966638560518</v>
+        <v>0.7197242944010752</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.1461611263275657</v>
+        <v>-0.3770051463660279</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1481305220316922</v>
+        <v>-0.368807070814595</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4000,7 +4000,7 @@
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.07366102874875759</v>
+        <v>-0.01905993200695977</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1528441524405048</v>
+        <v>-0.1920004187564906</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1471946877875379</v>
+        <v>-0.09026431658256608</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0977853992929627</v>
+        <v>-0.03630057464731017</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0633695606674405</v>
+        <v>0.09329937733204348</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.2026984663717152</v>
+        <v>0.01779347229585744</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,16 +4063,16 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.303193565739888</v>
+        <v>0.6503068879796733</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.08023883714610111</v>
+        <v>-0.2162474242862261</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1338554503019364</v>
+        <v>-0.07905657082738619</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -4081,85 +4081,85 @@
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1398377468101697</v>
+        <v>-0.2471066831538737</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.06420967484831724</v>
+        <v>0.2587409591283643</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.03853093079771222</v>
+        <v>-0.04488475502847725</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01185099354277087</v>
+        <v>-0.1847604533129718</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1074905016715049</v>
+        <v>0.4411228764762863</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1017836322112222</v>
+        <v>0.1646132057035102</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.130576763186451</v>
+        <v>-0.2461399505678538</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.1006319348116828</v>
+        <v>0.2625828764015151</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.04614396433447721</v>
+        <v>-0.01877057148602835</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,46 +4171,46 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.09693579429804144</v>
+        <v>-0.376739802675848</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.06218897889433424</v>
+        <v>0.1450845970803283</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.06200448919567968</v>
+        <v>-0.1232143288079706</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.01522923821981897</v>
+        <v>-0.1005822504190324</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.09305624298659931</v>
+        <v>0.05278050341796836</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.1245753163535222</v>
+        <v>0.02845507647043594</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,25 +4225,25 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0550020124549811</v>
+        <v>0.008200717623800728</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.02980452436472483</v>
+        <v>-0.2151138000872465</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.07478533683956096</v>
+        <v>-0.2144282586349133</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
@@ -4252,49 +4252,49 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1136577387338489</v>
+        <v>-0.2275213367635403</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0777499734688728</v>
+        <v>0.2491850430168686</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.07204926951424286</v>
+        <v>0.0009126892396255014</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1535539180305159</v>
+        <v>-0.1988059539612044</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.07361892816030186</v>
+        <v>0.115587827954521</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.02130428756263552</v>
+        <v>0.01838763393693323</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4303,46 +4303,46 @@
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1362508752574995</v>
+        <v>-0.3092328050614892</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.07729536289374792</v>
+        <v>0.3092438069515163</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.04549929567386099</v>
+        <v>-0.03918755474888756</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04545778187734946</v>
+        <v>-0.192553491699983</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.128863500034553</v>
+        <v>0.190847515051194</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.04835632130830609</v>
+        <v>0.04457464748400688</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
@@ -4351,61 +4351,61 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.01901674241117042</v>
+        <v>-0.04420849767019399</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.1007755355971119</v>
+        <v>0.1171460010017838</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.003998648680048871</v>
+        <v>0.04110298496383952</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.03864511982969442</v>
+        <v>-0.2910786718330293</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.1173324706521157</v>
+        <v>0.148009253467359</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,22 +4416,22 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3657294864590698</v>
+        <v>0.5187480455717686</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06839411686728575</v>
+        <v>-0.03314505428874063</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1881795368389593</v>
+        <v>-0.1235827170519788</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,25 +4443,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3482089244628186</v>
+        <v>0.7945450991965891</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06650991151649506</v>
+        <v>-0.1902506446047535</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.346435446478965</v>
+        <v>-0.1426552542408362</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -4470,7 +4470,7 @@
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.09379528030597573</v>
+        <v>0.223748411751409</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,64 +4479,64 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.06790868716935584</v>
+        <v>-0.1650339482037363</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04401100269575666</v>
+        <v>-0.0008464952570357867</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03252902186089951</v>
+        <v>0.04559965058583755</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.02315983523660043</v>
+        <v>-0.1504367209590921</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.006369503387716356</v>
+        <v>-0.08284799094764131</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.08150769383833242</v>
+        <v>0.2391337927437895</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.00241974365164512</v>
+        <v>0.11354500353428</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.1151080090335346</v>
+        <v>-0.1627783555558504</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,28 +4548,28 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4281433869428349</v>
+        <v>1.023711669116016</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.1086663308935397</v>
+        <v>-0.3158538211874206</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.2872056118960397</v>
+        <v>-0.3168125532708437</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.1169333763380754</v>
+        <v>0.001506099480069769</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,52 +4587,52 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.09554721055399787</v>
+        <v>-0.1193668679236256</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.06024200169568319</v>
+        <v>-0.06939221393665523</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1130831352205336</v>
+        <v>0.04867652580662084</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.005395970299287962</v>
+        <v>0.1674983933516316</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.02802567217115953</v>
+        <v>-0.05349227158611362</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2205941897360093</v>
+        <v>0.7175932858002372</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.0711807782769911</v>
+        <v>-0.1558185205513936</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.1011436130861831</v>
+        <v>-0.1916951784038764</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4659,7 +4659,7 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.1152138805048414</v>
+        <v>-0.321129175756475</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
@@ -4668,52 +4668,52 @@
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.02267636061497144</v>
+        <v>0.04530213740475298</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0996067999021835</v>
+        <v>0.1469680666232339</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01187254690033768</v>
+        <v>-0.4185313243276482</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.02534403456750108</v>
+        <v>0.2268550903869705</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.02327705574457894</v>
+        <v>0.2144305276738949</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.09782871045936212</v>
+        <v>-0.3072205780334089</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
@@ -4722,25 +4722,25 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.01726083727336404</v>
+        <v>0.004693314052451099</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.1130786542341605</v>
+        <v>0.122348961533954</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.1025299013921074</v>
+        <v>-0.04302246437055066</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04658813252711668</v>
+        <v>-0.3188686641676997</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-0.04678165012369367</v>
+        <v>-0.04425661843145102</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,31 +4761,31 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02181620679931375</v>
+        <v>-0.1843038499591856</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.001382878384361716</v>
+        <v>0.03345416656573567</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.003078041075038944</v>
+        <v>-0.03422977571471376</v>
       </c>
       <c r="DT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4794,19 +4794,19 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.07832679000541</v>
+        <v>0.1001368910728698</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.02790307995403161</v>
+        <v>0.0006871420846235865</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.06073025862337283</v>
+        <v>-0.1595884640017049</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4818,25 +4818,25 @@
         <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.08277365153212229</v>
+        <v>-0.03119548203577478</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.02362564249326308</v>
+        <v>-0.1110819998265371</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.09448095575954674</v>
+        <v>0.06721845141776389</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
@@ -4845,37 +4845,37 @@
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.04130795210460136</v>
+        <v>-0.1041018116235769</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.02828903146425448</v>
+        <v>-0.1870649355500025</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.06404034836998941</v>
+        <v>0.08390219255350619</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.09788838961276468</v>
+        <v>-0.3481648110816913</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
@@ -4884,52 +4884,52 @@
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.01899407976525673</v>
+        <v>0.001264733495027976</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.1026126039976169</v>
+        <v>0.1186354829971972</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.03551069325321764</v>
+        <v>-0.3576025041459998</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.04579582130306877</v>
+        <v>0.209585088672687</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.09056353873254956</v>
+        <v>0.09774185468126115</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.01611264805669968</v>
+        <v>-0.07774363186778538</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,10 +4938,10 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.01478243666442915</v>
+        <v>0.03699309717389494</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.05498046655220845</v>
+        <v>0.1346722647818717</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4950,16 +4950,16 @@
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01403983031796241</v>
+        <v>-0.1045553730643966</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
@@ -4968,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.08193779274621041</v>
+        <v>-0.05131437863245858</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4977,7 +4977,7 @@
         <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1819249695443998</v>
+        <v>0.01056960836112063</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,52 +5563,52 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1236732909722768</v>
+        <v>-0.001857172280105538</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01715771429415033</v>
+        <v>-0.002521562618985243</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1438074904924797</v>
+        <v>0.01597844682056888</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1368090607276144</v>
+        <v>-0.007936605710025113</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.08955208101586677</v>
+        <v>-0.007177263186099055</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1293026015852562</v>
+        <v>0.007449125673309957</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,34 +5617,34 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02655591892497395</v>
+        <v>-0.007644403505499099</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0459169655337418</v>
+        <v>-0.005125541527716228</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.05106625154745337</v>
+        <v>-0.0008074453409418858</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.04233663002643779</v>
+        <v>-0.002026766415994774</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,43 +5653,43 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.01432198939914193</v>
+        <v>0.0006979605710745391</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.07355747839674054</v>
+        <v>0.005400892938287158</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.05894265807356858</v>
+        <v>0.0007661496594237219</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.03109227468661841</v>
+        <v>-0.002190719228017155</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3818194874799127</v>
+        <v>0.01909163009715889</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,16 +5698,16 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.005857681383452188</v>
+        <v>-0.004800465221563892</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.09697951834347503</v>
+        <v>-0.004706696170732486</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.01441968337592178</v>
+        <v>-0.00327596054177514</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,16 +5725,16 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1259123241836561</v>
+        <v>-0.007189060226139903</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.06684251110680441</v>
+        <v>0.0001276907269430572</v>
       </c>
       <c r="BK10" t="n">
         <v>-0</v>
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.157317737381399</v>
+        <v>0.005969970284814503</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,43 +5752,43 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1151401530469654</v>
+        <v>0.01056190663202032</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.03981593109577158</v>
+        <v>0.00317478338419435</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2230904411210927</v>
+        <v>0.01356980120765218</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.02425229819454231</v>
+        <v>-0.003414826527047658</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.05943959064277363</v>
+        <v>-0.007170499372444656</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5797,70 +5797,70 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.0494967304706723</v>
+        <v>-0.003354701183564777</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.02332221838328587</v>
+        <v>0.00166414277454713</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.001636410140198058</v>
+        <v>0.001292160701819012</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.0572873830613316</v>
+        <v>-0.003096368791147751</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.09700534762258919</v>
+        <v>0.007156864461751176</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0.00745422773922443</v>
+        <v>0.0001845618418085858</v>
       </c>
       <c r="CU10" t="n">
         <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02856013628736857</v>
+        <v>-0.003378939729930202</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.008787862474600235</v>
+        <v>0.002115579502028379</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,34 +5869,34 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.009769210490675848</v>
+        <v>0.002586701669343433</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.1929985811245455</v>
+        <v>-0.0007343337977885009</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.03491680683850694</v>
+        <v>-0.002437081979158945</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.06071958972047854</v>
+        <v>0.001890104809450288</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
@@ -5905,52 +5905,52 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.01380690399518678</v>
+        <v>-0.005771556665172019</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.02131256248581367</v>
+        <v>-0.004652678129635114</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.03830080802191736</v>
+        <v>0.001031939555131653</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.05173202239329228</v>
+        <v>0.00497320814007411</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.004909705778297758</v>
+        <v>-0.004656674969338372</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.02692790911581827</v>
+        <v>-0.004972128693964135</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
@@ -5959,16 +5959,16 @@
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.003166032853117174</v>
+        <v>0.001777515555501562</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.05328371366092356</v>
+        <v>-0.002036291841283806</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.008900768520514923</v>
+        <v>-0.001784488648737088</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
@@ -5986,16 +5986,16 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.0329242504851982</v>
+        <v>0.0001175269733140911</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.001746343506336179</v>
+        <v>-0.001012787667986705</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
@@ -6004,25 +6004,25 @@
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.00463320504920417</v>
+        <v>0.002261144009723561</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.03430092639998676</v>
+        <v>-0.003810116353215954</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.005697296617986074</v>
+        <v>0.0001232261694322166</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,16 +6031,16 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.004396661817360158</v>
+        <v>0.002543976605497585</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.003149871498446935</v>
+        <v>0.000785696063473227</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,25 +6049,25 @@
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03272695008061028</v>
+        <v>0.006180287872263083</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.0240846452678207</v>
+        <v>-0.002141580732414737</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.00108068990127986</v>
+        <v>-0.0008533366782065576</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,25 +6076,25 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.002771654628233284</v>
+        <v>0.001653058364893642</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.05505259410226756</v>
+        <v>0.00294591964259228</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.08616681316232211</v>
+        <v>-0.005454965129879252</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.0679923754594853</v>
+        <v>-0.000167770315735016</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
@@ -6120,19 +6120,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.1791919348224608</v>
+        <v>-0.05693354837672451</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5639306159272277</v>
+        <v>0.07305372485506198</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1569250848848328</v>
+        <v>-0.007685443689653116</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6147,22 +6147,22 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1561438142739711</v>
+        <v>-0.04956871964647539</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4562202169458763</v>
+        <v>0.1112705784661589</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2666690829447152</v>
+        <v>-0.008800675559064776</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
@@ -6174,52 +6174,52 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02468212405635917</v>
+        <v>0.01479643486619234</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2636790850092571</v>
+        <v>0.01444980912778653</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.05073432589376828</v>
+        <v>0.00567683736881631</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0046905913438237</v>
+        <v>-0.001256784958473466</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.06192614682503022</v>
+        <v>0.003443489256553327</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.03452846563732</v>
+        <v>-0.01070618873078982</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
@@ -6228,10 +6228,10 @@
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.07714913431952598</v>
+        <v>-0.007221501314939064</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2257422126304688</v>
+        <v>0.03047114371199717</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,52 +6240,52 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.07173871562920486</v>
+        <v>-0.01091341625081675</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.09478822686065329</v>
+        <v>-0.01661181683169147</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.6044136041103734</v>
+        <v>0.08700976266773011</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1639171342912727</v>
+        <v>-0.03021809340268844</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.1070778673736435</v>
+        <v>-0.04859169910652177</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03440261434493155</v>
+        <v>0.01214414413820694</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,13 +6294,13 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.3083215869627891</v>
+        <v>-0.02185458381583994</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.03221055847867669</v>
+        <v>0.009819494749668199</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.004339874276946113</v>
+        <v>0.03099069692789448</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.07535665308074861</v>
+        <v>0.0335218825498003</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,73 +6336,73 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.06826084222509536</v>
+        <v>0.009013002689791551</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.4287880064342371</v>
+        <v>0.07703500761120112</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.01986712985986684</v>
+        <v>-0.003823686860642059</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.04728291891603534</v>
+        <v>0.02503693110857505</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1310783522400944</v>
+        <v>-0.03457977775036721</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0005417181817210708</v>
+        <v>-0.005167830881459804</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.1305272506628601</v>
+        <v>-0.0006021452113580491</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.004571644278204876</v>
+        <v>-0.05131653587323786</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1182351449909031</v>
+        <v>0.00883491740153469</v>
       </c>
       <c r="CR11" t="n">
         <v>-0</v>
@@ -6414,22 +6414,22 @@
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.03025726478000201</v>
+        <v>0.02165024508449366</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1400299182681987</v>
+        <v>-0.03493917076895336</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.01378355496369901</v>
+        <v>-0.01127948371698145</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6438,70 +6438,70 @@
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.06784581980570151</v>
+        <v>0.0219381177983869</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.2520139766884002</v>
+        <v>-0.0499435544028364</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.1239456053693779</v>
+        <v>-0.02565834032918567</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.0733090323827689</v>
+        <v>-0.009682829162003279</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.09250805637071231</v>
+        <v>-0.02396890660708502</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.02233105825250162</v>
+        <v>0.002506603036828708</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0.01705921154912454</v>
+        <v>0.01884557340426199</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1377384365257819</v>
+        <v>0.02514763866987171</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,40 +6510,40 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.108475428887293</v>
+        <v>0.01151653832948076</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.02441416115951488</v>
+        <v>0.01481152421454514</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.01090899546804556</v>
+        <v>-0.008241779300631717</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.001742481280514947</v>
+        <v>-0.01658120299723398</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
@@ -6552,19 +6552,19 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.01220715882993608</v>
+        <v>0.00938459284655894</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1070567256948414</v>
+        <v>-0.01525318946493738</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.0450217876104428</v>
+        <v>-0.01535774956216675</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6573,43 +6573,43 @@
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.02544321985770457</v>
+        <v>0.02583613834875438</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1463674076943453</v>
+        <v>-0.04361920380505448</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.05222289013059514</v>
+        <v>-0.01013855283502112</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.05210003148994166</v>
+        <v>0.01226778258076928</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.05920602867081445</v>
+        <v>-0.01295294585695251</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,7 +6618,7 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.09423036057038529</v>
+        <v>0.006170803064064716</v>
       </c>
       <c r="FL11" t="n">
         <v>0</v>
@@ -6630,40 +6630,40 @@
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0.01418227947051117</v>
+        <v>-0.01273260489572294</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.03782360245113797</v>
+        <v>0.004644412617024408</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.007698338626467181</v>
+        <v>0.009512830060899282</v>
       </c>
       <c r="FU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.113090835870834</v>
+        <v>0.007361556336805412</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.02181073007780042</v>
+        <v>-0.02481918824880776</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
@@ -6675,16 +6675,16 @@
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF11" t="n">
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,22 +6692,22 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3141962187878294</v>
+        <v>0.004711578066475666</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.07965497230429107</v>
+        <v>-0.002880926032843495</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2520574303727279</v>
+        <v>-0.001724628392335074</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -6716,25 +6716,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2029192847236026</v>
+        <v>0.006906433512453601</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1274704508985705</v>
+        <v>-0.003225256454613636</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2246428084239588</v>
+        <v>-0.002798315362737132</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6746,22 +6746,22 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1390305706167526</v>
+        <v>0.0004988410268500516</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1920124868043915</v>
+        <v>-0.001144908403137987</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.07398348455169612</v>
+        <v>0.0002597597329352654</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
@@ -6773,61 +6773,61 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.07746991571396653</v>
+        <v>-0.0001723413709749378</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.02414407405784648</v>
+        <v>-0.0005283575003602616</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.004577041267343496</v>
+        <v>1.240124341745298e-05</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.04085117864429864</v>
+        <v>0.002382018935217481</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.03209072455359955</v>
+        <v>0.0003966670010391829</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.08668679827402018</v>
+        <v>-0.0003646840126468244</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.466916837700897</v>
+        <v>0.008368493858241731</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,16 +6836,16 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08796955936699147</v>
+        <v>-0.0007199098936017686</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.1342366813317483</v>
+        <v>-0.000706034313073906</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,7 +6854,7 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.07784245899221844</v>
+        <v>-0.002411482242784002</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,25 +6863,25 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.09965468088573445</v>
+        <v>-0.002192286030832893</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.1595252828882028</v>
+        <v>-0.0006259612898247905</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.07246932528683199</v>
+        <v>0.0003676903170955589</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
@@ -6890,13 +6890,13 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1894592880494755</v>
+        <v>0.004178193164124496</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.05826515204510624</v>
+        <v>0.0006377317189311326</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1983862996125943</v>
+        <v>0.005707527467292053</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0289968579173603</v>
+        <v>-0.001211939200314257</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0.07148621133650572</v>
+        <v>-0.0002945650992209818</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.09970851100070367</v>
+        <v>-0.002269359145785661</v>
       </c>
       <c r="CF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.02102410920510392</v>
+        <v>0.001238373127623219</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.06256144198409963</v>
+        <v>0.0002977592382515328</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6959,25 +6959,25 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.1206839598311869</v>
+        <v>-0.002654854325138197</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
         <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.05018782407644743</v>
+        <v>5.609862141161087e-05</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0.02569067621355014</v>
+        <v>-0.0009282834059671729</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,10 +6986,10 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.07844234247562724</v>
+        <v>-0.002444609747983776</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
@@ -6998,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.02648955331951159</v>
+        <v>0.0009045151885893391</v>
       </c>
       <c r="DA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.06314365264422182</v>
+        <v>0.000717743055789784</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7013,10 +7013,10 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.3009308382715615</v>
+        <v>-0.001337948691891303</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
@@ -7025,16 +7025,16 @@
         <v>-0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04763117500854867</v>
+        <v>-0.0005408089451481496</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0.03434545992759726</v>
+        <v>-0.001033541000443559</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>-0</v>
@@ -7043,49 +7043,49 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.03509949557107733</v>
+        <v>-0.000795070897465198</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.02567262786137329</v>
+        <v>0.0007517231080709781</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0.006511314379098037</v>
+        <v>0.0009518806541144609</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.09745524173904928</v>
+        <v>0.001805996455460206</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.05949998106997276</v>
+        <v>-0.0008708166851840916</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.01120081521102696</v>
+        <v>0.0003546001847332635</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7094,25 +7094,25 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02011899954806808</v>
+        <v>-0.001721024112785019</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05910464627298774</v>
+        <v>0.001112396675041418</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.05286623130024803</v>
+        <v>-0.0003597781779178526</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7121,52 +7121,52 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.05081734296801985</v>
+        <v>-0.001408568622134857</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.03383228058868606</v>
+        <v>-0.0002885299731218161</v>
       </c>
       <c r="ET12" t="n">
         <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.005451265370635421</v>
+        <v>-0.0003084803052827901</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.08865955909886018</v>
+        <v>-0.002679176669194908</v>
       </c>
       <c r="EZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0240705472505908</v>
+        <v>0.0006618380775404021</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.05616340269385676</v>
+        <v>0.0002960836744509416</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,25 +7175,25 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.03653141542470963</v>
+        <v>-0.0006467817392557213</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.09958907644181338</v>
+        <v>0.0002081232651516518</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.05455782872947018</v>
+        <v>-0.0002398983696928803</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
@@ -7202,10 +7202,10 @@
         <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.006113286606359535</v>
+        <v>-0.0002191715216604927</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,28 +7214,28 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01491585518422214</v>
+        <v>0.0001419452674765809</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0211869294295657</v>
+        <v>0.001009109470158349</v>
       </c>
       <c r="FW12" t="n">
         <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.1073687230834899</v>
+        <v>-0.00218537916019956</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7244,10 +7244,10 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.05363638811273655</v>
+        <v>0.0008550703286128896</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6611070049647433</v>
+        <v>1.387818466047781</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.221708115772521</v>
+        <v>-0.5554324757905313</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2875214056495199</v>
+        <v>-0.1388280071306726</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4991847486623592</v>
+        <v>1.77630875419859</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2338720022007768</v>
+        <v>-0.6447861005670303</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -7306,16 +7306,16 @@
         <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.2780759479942315</v>
+        <v>-0.09901648737086287</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2293431218561694</v>
+        <v>0.3122410191937965</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
@@ -7324,88 +7324,88 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.01406932831640743</v>
+        <v>-0.2105800304681103</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.04411210728502353</v>
+        <v>-0.338653297542895</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.09049171441047234</v>
+        <v>0.05703218787740014</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.0200433384301381</v>
+        <v>-0.1174323317648389</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.01284152924263971</v>
+        <v>0.03966122005600162</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1309826418733031</v>
+        <v>0.7197253285493376</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01246450937336107</v>
+        <v>0.3377091666068554</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.02076091529902857</v>
+        <v>-0.009510455507345823</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.6658466140207575</v>
+        <v>2.059644388494239</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0365461582636193</v>
+        <v>-0.3427001051777899</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7414,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.20497059061077</v>
+        <v>0.05956894172015696</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.137733942557748</v>
+        <v>-0.4581231591492498</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.2737994952142661</v>
+        <v>-0.4996255000353634</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
         <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.1700186501196783</v>
+        <v>-0.0646154878964891</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.003398279316126802</v>
+        <v>0.08738307356410632</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,25 +7459,25 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.2265337423467342</v>
+        <v>0.2803154810317048</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0.01539210454081764</v>
+        <v>0.199091054394245</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.424386194220776</v>
+        <v>1.404716266361656</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,25 +7486,25 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.05589786016732926</v>
+        <v>-0.2684920068544697</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0.07339282788126911</v>
+        <v>-0.2386038994357862</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1711671489911168</v>
+        <v>-0.7402729230744921</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
@@ -7513,37 +7513,37 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.007442893568902368</v>
+        <v>0.143309296253392</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.111634190885885</v>
+        <v>0.07458205376188978</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.102347380409753</v>
+        <v>-0.7177578427275473</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.1171929494889142</v>
+        <v>0.1336721310149253</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7552,40 +7552,40 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.03562078239710942</v>
+        <v>0.01154503248470809</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1435897549165399</v>
+        <v>-0.7171852499585787</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.01217594077982391</v>
+        <v>0.09979409777338172</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.09528744497502825</v>
+        <v>0.151007176979053</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.3120649377944213</v>
+        <v>-0.3165678553010046</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
@@ -7594,7 +7594,7 @@
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.07768592272902651</v>
+        <v>-0.02844424912976416</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7603,43 +7603,43 @@
         <v>0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.04279746168229106</v>
+        <v>-0.1633727606372222</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.06108808038065231</v>
+        <v>-0.3482375218868322</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.0314644624894547</v>
+        <v>0.02352194088418457</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0.02536125210831234</v>
+        <v>-0.3029509100379154</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1498024623319651</v>
+        <v>0.3928034022453869</v>
       </c>
       <c r="DY13" t="n">
         <v>-0</v>
@@ -7648,25 +7648,25 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.07154350706011629</v>
+        <v>-0.2082161522971257</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0207493289882943</v>
+        <v>0.2672124957101829</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03700984611373843</v>
+        <v>-0.3761827585435852</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,37 +7675,37 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0342036265036386</v>
+        <v>-0.03888226384296234</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.1478980856562433</v>
+        <v>0.05437255059658801</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1102814231996389</v>
+        <v>-0.4828198183622295</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.0008521424464893216</v>
+        <v>0.04876223593887938</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7714,13 +7714,13 @@
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.05736264502081628</v>
+        <v>0.1441552541371945</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1747296281953986</v>
+        <v>-0.8232906475191788</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
@@ -7729,25 +7729,25 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.001902126309941888</v>
+        <v>0.09300267116306613</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.09083857049553946</v>
+        <v>0.1494667488676598</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.08757933447152355</v>
+        <v>-0.322339893357141</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.05145068386895031</v>
+        <v>-0.05559516688589251</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.06691080776893746</v>
+        <v>-0.2472796486865969</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.02335293562350097</v>
+        <v>-0.06371319003411205</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,46 +7783,46 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.005961776654565138</v>
+        <v>0.05450735313290975</v>
       </c>
       <c r="FU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW13" t="n">
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01848169202479064</v>
+        <v>-0.3216977069022018</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.1551075564648476</v>
+        <v>-0.4035425476323808</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0.01837381666242189</v>
+        <v>0.1631101415725155</v>
       </c>
     </row>
     <row r="14">
@@ -8396,19 +8396,19 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.6871197174934727</v>
+        <v>-0.6401809149151384</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5543976346125383</v>
+        <v>0.2644749802075946</v>
       </c>
       <c r="D15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3878385524627435</v>
+        <v>0.3923135086994322</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
@@ -8423,28 +8423,28 @@
         <v>-0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5122977271864013</v>
+        <v>-0.8586535761814341</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3893630872254163</v>
+        <v>0.2336002626468143</v>
       </c>
       <c r="M15" t="n">
         <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.478315359295838</v>
+        <v>0.3330339402826668</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
@@ -8453,16 +8453,16 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2166839902136527</v>
+        <v>-0.1963631364902726</v>
       </c>
       <c r="U15" t="n">
-        <v>0.005740263514818372</v>
+        <v>-0.1372929055289709</v>
       </c>
       <c r="V15" t="n">
         <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.002042858943735593</v>
+        <v>-0.08570714067835884</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -8471,52 +8471,52 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1258866522558539</v>
+        <v>-0.03738491825364589</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.001548571214797603</v>
+        <v>0.1344010307947075</v>
       </c>
       <c r="AE15" t="n">
         <v>-0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.02274473615630553</v>
+        <v>0.0466915587380534</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.3445018676425765</v>
+        <v>-0.367345771506878</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.02578373018405311</v>
+        <v>0.04189077532303796</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.003001119579601787</v>
+        <v>-0.3490575230621038</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
@@ -8525,7 +8525,7 @@
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
@@ -8534,43 +8534,43 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.7201474040910649</v>
+        <v>-0.9450202576882437</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.4046632370302981</v>
+        <v>-0.03774586994741099</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1267976712711924</v>
+        <v>-0.07915313655692441</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.09835320827333748</v>
+        <v>0.4426839614578791</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.1372511516076264</v>
+        <v>0.2709294287695689</v>
       </c>
       <c r="BF15" t="n">
         <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.548083008600826</v>
+        <v>0.6668288641241157</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -8588,25 +8588,25 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.184901326902421</v>
+        <v>0.01019715480671682</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.08910230487413472</v>
+        <v>-0.01472742480812462</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.08627015295746959</v>
+        <v>-0.05391131844788495</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
         <v>0</v>
@@ -8615,16 +8615,16 @@
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.3508908179268797</v>
+        <v>-0.6191486365411082</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.4529280836974802</v>
+        <v>-0.04710945432729154</v>
       </c>
       <c r="BX15" t="n">
         <v>-0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.05645949786646896</v>
+        <v>-0.0497886731514195</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -8636,31 +8636,31 @@
         <v>-0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1503794137220025</v>
+        <v>0.3668896315770751</v>
       </c>
       <c r="CF15" t="n">
-        <v>-0.07479569953581507</v>
+        <v>-0.0848711628163194</v>
       </c>
       <c r="CG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.1213342912226954</v>
+        <v>-0.1015863901917128</v>
       </c>
       <c r="CI15" t="n">
         <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -8669,16 +8669,16 @@
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.04672080895384569</v>
+        <v>0.320933565449458</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.005323350864917712</v>
+        <v>-0.04379019373742597</v>
       </c>
       <c r="CP15" t="n">
         <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1254596263353354</v>
+        <v>-0.1581695900951164</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
@@ -8696,16 +8696,16 @@
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.07757006486998717</v>
+        <v>0.3355240629012689</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0.06258736522237045</v>
+        <v>-0.06962499259440655</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.07102674800776251</v>
+        <v>-0.07786071741255918</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
@@ -8714,7 +8714,7 @@
         <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>-0</v>
@@ -8723,16 +8723,16 @@
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1256735935008087</v>
+        <v>0.02509392398859874</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.08065943002301712</v>
+        <v>0.03870160978666754</v>
       </c>
       <c r="DH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.08473206207730728</v>
+        <v>0.02415353930918912</v>
       </c>
       <c r="DJ15" t="n">
         <v>0</v>
@@ -8744,52 +8744,52 @@
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.002332447711510046</v>
+        <v>0.153657120820286</v>
       </c>
       <c r="DP15" t="n">
-        <v>-0.0747793725964658</v>
+        <v>-0.04928786646305319</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.1155439079874828</v>
+        <v>-0.08940053827879814</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.01209923124503321</v>
+        <v>-0.251526974605572</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.1263090897489462</v>
+        <v>-0.02753064561270863</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.127131667680542</v>
+        <v>0.20875180901856</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
@@ -8801,46 +8801,46 @@
         <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.06713534067916076</v>
+        <v>0.201084795562736</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0.03215473614290085</v>
+        <v>0.09785086249834941</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.1550726988351456</v>
+        <v>-0.08061784382251405</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM15" t="n">
         <v>0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.005535848430969405</v>
+        <v>0.2579433556211138</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.116978227838612</v>
+        <v>0.1008068814849279</v>
       </c>
       <c r="ER15" t="n">
         <v>0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.07506344265449706</v>
+        <v>-0.03955844725748849</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
@@ -8849,34 +8849,34 @@
         <v>0</v>
       </c>
       <c r="EV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.08474417053609594</v>
+        <v>0.397157745714747</v>
       </c>
       <c r="EZ15" t="n">
-        <v>-0.057961560032683</v>
+        <v>-0.0714631926711963</v>
       </c>
       <c r="FA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.09568343397529462</v>
+        <v>-0.1045444281336502</v>
       </c>
       <c r="FC15" t="n">
         <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>0</v>
@@ -8885,43 +8885,43 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.188635731691157</v>
+        <v>0.06111499463675421</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.1747378483227353</v>
+        <v>0.2598791586891818</v>
       </c>
       <c r="FJ15" t="n">
         <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.2264260631060674</v>
+        <v>0.2594721292342434</v>
       </c>
       <c r="FL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>5.604298610681453e-05</v>
+        <v>0.001170562888871476</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0.06382797337706593</v>
+        <v>-0.01422541217158537</v>
       </c>
       <c r="FS15" t="n">
         <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.01119998333724158</v>
+        <v>-0.01467743021668013</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
@@ -8930,25 +8930,25 @@
         <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
         <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.09716828696710172</v>
+        <v>0.1762655344617944</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0.08856369978012235</v>
+        <v>0.2018672849884998</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
         <v>0</v>
@@ -8957,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
         <v>-0</v>
@@ -8965,10 +8965,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1866719415801081</v>
+        <v>0.3334468111427852</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05829264228796881</v>
+        <v>-0.009269994688488731</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.09678038700810594</v>
+        <v>-0.1722743192724902</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
@@ -8992,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1554348635085714</v>
+        <v>0.4274677947742208</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,67 +9004,67 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.02892201020995755</v>
+        <v>-0.1226461785227399</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.08240097225374268</v>
+        <v>-0.2066187002240427</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.02443768408640635</v>
+        <v>0.1382811658854516</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.02147389258140084</v>
+        <v>-0.06509389007760147</v>
       </c>
       <c r="X16" t="n">
-        <v>0.004927890255003738</v>
+        <v>-0.03238252194945517</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.005025541633019228</v>
+        <v>-0.05432972687622611</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01013793594481165</v>
+        <v>-0.1282906431013296</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.002847930542641288</v>
+        <v>0.02359952134139547</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9073,10 +9073,10 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.02573905422030843</v>
+        <v>0.09836997295232357</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
@@ -9085,13 +9085,13 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.0002167393453264373</v>
+        <v>-0.04219413694993862</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.04255094142916818</v>
+        <v>-0.04841546062649761</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9100,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1300306862304568</v>
+        <v>0.5945863470320031</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
@@ -9112,25 +9112,25 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.03454946183637714</v>
+        <v>-0.2225169276374627</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.0932891712073569</v>
+        <v>-0.2253813884603843</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.04168909320494315</v>
+        <v>-0.1440256885487241</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,106 +9139,106 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.04610203480945364</v>
+        <v>-0.0383548166607523</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.02763563012009701</v>
+        <v>-0.04203315590481461</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
         <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0302141482276657</v>
+        <v>0.1037039798622061</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.008425782294603714</v>
+        <v>0.04130945210457534</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.0110753624257428</v>
+        <v>0.02349801805649007</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.06826351040113088</v>
+        <v>0.3550449900908063</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.02672982968890681</v>
+        <v>-0.05578811646106815</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.02402262984171773</v>
+        <v>-0.09987020979428983</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.03584356157458097</v>
+        <v>-0.1206376677182342</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0004711392407818426</v>
+        <v>0.04108805820587651</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02644550832374689</v>
+        <v>0.05092563744122024</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.003009996148552152</v>
+        <v>-0.1661478876505366</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,37 +9247,37 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.004235462552216493</v>
+        <v>0.128814514966564</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.0252412651602634</v>
+        <v>0.02940660715833415</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.03304796974554574</v>
+        <v>-0.1193841144472933</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>9.521726397696762e-05</v>
+        <v>0.01960763109640123</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03174898807406948</v>
+        <v>0.08469116424084934</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9286,40 +9286,40 @@
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.02393445624037073</v>
+        <v>-0.1212081939997435</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04725598870191916</v>
+        <v>-0.1124080766166522</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.0005184237985485618</v>
+        <v>0.04133662051679975</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.009849863498218285</v>
+        <v>-0.03620886298931333</v>
       </c>
       <c r="DP16" t="n">
         <v>0</v>
@@ -9328,16 +9328,16 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.02102028348500859</v>
+        <v>0.01439047086687922</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.001705998930743725</v>
+        <v>0.07094099661598575</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
@@ -9346,22 +9346,22 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.02798800554246751</v>
+        <v>-0.09478388450390221</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.00400238244854873</v>
+        <v>0.006437962203060496</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.01192266688131346</v>
+        <v>0.05383555967544514</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
         <v>0</v>
@@ -9373,49 +9373,49 @@
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.03796831465226183</v>
+        <v>-0.03104875330270898</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.009914527201774343</v>
+        <v>-0.002835190304277794</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.03520724016980342</v>
+        <v>-0.03018698438483594</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO16" t="n">
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.02297504104250167</v>
+        <v>-0.02373925244083763</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.008699797892150937</v>
+        <v>-0.08255964785007794</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.003565592136047243</v>
+        <v>0.00665056295597038</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
@@ -9427,34 +9427,34 @@
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.03122900648766589</v>
+        <v>-0.1443221510453787</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.0006733554488430249</v>
+        <v>0.009990029221974842</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02785395217244502</v>
+        <v>0.0639011919994734</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.004936412956989913</v>
+        <v>0.1309515176222361</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,25 +9463,25 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.01017082049156274</v>
+        <v>-0.06953736219376644</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.02911004224525092</v>
+        <v>0.1214342107850361</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.002385368259483431</v>
+        <v>-0.04193578746791882</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,37 +9490,37 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.01202217662138222</v>
+        <v>0.08026402979739294</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.01970442075799006</v>
+        <v>-0.09950410882917209</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.0005534571715125191</v>
+        <v>-0.04612045933316121</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.015246041461427</v>
+        <v>0.1224477342348159</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
@@ -9529,7 +9529,7 @@
         <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1194034427030947</v>
+        <v>0.1841047817589332</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,37 +9546,37 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09116545916255502</v>
+        <v>-0.05195931522785008</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.02237423886340071</v>
+        <v>-0.04536911089783013</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08586486833385644</v>
+        <v>0.2067982323122322</v>
       </c>
       <c r="L17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.07314236435640335</v>
+        <v>-0.09387164268423372</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.02862672687352671</v>
+        <v>-0.06045638107117182</v>
       </c>
       <c r="P17" t="n">
         <v>-0</v>
@@ -9588,10 +9588,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.020689658951752</v>
+        <v>0.05979311624533098</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -9600,37 +9600,37 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.003645303850831054</v>
+        <v>-0.05254497406348722</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01224493385390129</v>
+        <v>0.00245393222088419</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.005024203859306907</v>
+        <v>-0.02090572167216067</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.002856713227994666</v>
+        <v>-0.08523795191223137</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.003622460907887978</v>
+        <v>0.01285905072605905</v>
       </c>
       <c r="AH17" t="n">
         <v>-0</v>
@@ -9642,37 +9642,37 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01903091436823276</v>
+        <v>0.01938288284594101</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01323768279170995</v>
+        <v>-0.04148858569838502</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.01252021794944855</v>
+        <v>0.009987829767859228</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT17" t="n">
         <v>-0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.09589795725253622</v>
+        <v>0.2182601519526247</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
@@ -9681,10 +9681,10 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.05156554550425667</v>
+        <v>-0.1556304504634594</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.01259778355051589</v>
+        <v>-0.08805109217741493</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -9693,13 +9693,13 @@
         <v>-0</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0219349691945563</v>
+        <v>-0.02909807220557964</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,52 +9708,52 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.05032069308723638</v>
+        <v>-0.004063389088104141</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.01910255917002472</v>
+        <v>-0.0006229681747091333</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.02692297810235758</v>
+        <v>0.03344083768311148</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01581246009888596</v>
+        <v>0.05059543624817734</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.02217476390530027</v>
+        <v>-0.002540814801700121</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.05172526683461891</v>
+        <v>0.1339037935946095</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -9762,10 +9762,10 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.02336839001696728</v>
+        <v>-0.05081169649446181</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.002075848900190223</v>
+        <v>-0.02712054306097722</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9780,34 +9780,34 @@
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.01944482579069419</v>
+        <v>-0.04695350503403033</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.01243818607272533</v>
+        <v>0.03488077269395234</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.007210200030520971</v>
+        <v>0.02111149761130328</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>-0</v>
       </c>
       <c r="CL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.00111584625061713</v>
+        <v>-0.03796807034559618</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,37 +9816,37 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.005734751937682209</v>
+        <v>0.08308994122917106</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.004238952934040293</v>
+        <v>0.02050702013086326</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.01234235461880544</v>
+        <v>-0.04790341597890908</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.009228165611734706</v>
+        <v>0.02893318137581526</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.0127615061201673</v>
+        <v>0.03505765327022203</v>
       </c>
       <c r="DB17" t="n">
         <v>-0</v>
@@ -9861,19 +9861,19 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.01716673692919502</v>
+        <v>-0.03326021641376366</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.01956647780585741</v>
+        <v>-0.05800854337807435</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.00319976311913611</v>
+        <v>0.01612237702245364</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
@@ -9882,40 +9882,40 @@
         <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.008796128107282041</v>
+        <v>-0.001789725876223108</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01862631149641674</v>
+        <v>-0.02900703715162709</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.01325797498010334</v>
+        <v>-0.003124824657584084</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.017059598554579</v>
+        <v>0.001598302860281959</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
@@ -9924,16 +9924,16 @@
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0149601860172486</v>
+        <v>-0.01797482294897518</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.001405673571006225</v>
+        <v>-0.0008767952505543481</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE17" t="n">
         <v>-0</v>
@@ -9942,22 +9942,22 @@
         <v>0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.01957291312824895</v>
+        <v>-0.0269747248307484</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.01106508156434093</v>
+        <v>0.02643458219272407</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.006668001882128687</v>
+        <v>0.0002375456909936139</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
@@ -9969,19 +9969,19 @@
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.0002485686429716852</v>
+        <v>-0.02052234475004467</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.008967056606943368</v>
+        <v>0.02006497100911928</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0.001015382227085778</v>
+        <v>0.04769477199384609</v>
       </c>
       <c r="EU17" t="n">
         <v>0</v>
@@ -9990,25 +9990,25 @@
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
         <v>0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.01258769146324386</v>
+        <v>-0.05532458567874643</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.01175031275618319</v>
+        <v>0.02421753334156102</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.0145820892315244</v>
+        <v>0.0192194006167046</v>
       </c>
       <c r="FD17" t="n">
         <v>0</v>
@@ -10020,10 +10020,10 @@
         <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.003731747530845433</v>
+        <v>0.07282834766442334</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
@@ -10032,16 +10032,16 @@
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.01405990522316315</v>
+        <v>-0.05436750503678876</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.0107423003744441</v>
+        <v>0.03968997414586103</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
@@ -10050,52 +10050,52 @@
         <v>0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.00270756418281065</v>
+        <v>-0.02144699782904914</v>
       </c>
       <c r="FR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.008823429105726883</v>
+        <v>0.03137118246449045</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.01174531979410375</v>
+        <v>-0.03681728599511318</v>
       </c>
       <c r="FV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.000598404594241947</v>
+        <v>-0.04705829026236159</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.01452772624249616</v>
+        <v>0.04094896159398116</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG17" t="n">
         <v>0</v>
@@ -10106,46 +10106,46 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4612862467944705</v>
+        <v>0.2285593605166132</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.09930328045141679</v>
+        <v>-0.1784469776782319</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.157128459823017</v>
+        <v>0.003598621590887574</v>
       </c>
       <c r="F18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3447047673074812</v>
+        <v>0.2761791401045291</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.125967975384701</v>
+        <v>-0.2302347667805673</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1560561176498687</v>
+        <v>-0.05747701549487868</v>
       </c>
       <c r="O18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>-0</v>
@@ -10157,73 +10157,73 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.106869743431187</v>
+        <v>0.05788614314431585</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01859818000135718</v>
+        <v>-0.02638144319304299</v>
       </c>
       <c r="W18" t="n">
-        <v>0.08160149662149267</v>
+        <v>-0.03452700892547066</v>
       </c>
       <c r="X18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1100425264058356</v>
+        <v>-0.03537863239777373</v>
       </c>
       <c r="AD18" t="n">
         <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.005021727526381743</v>
+        <v>-0.03434501862260045</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.01254571869196717</v>
+        <v>-0.07805361056550156</v>
       </c>
       <c r="AG18" t="n">
         <v>-0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.006215914120162379</v>
+        <v>0.05713462236369259</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.06200841123069645</v>
+        <v>-0.04520491048334267</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.0895042480861834</v>
+        <v>0.009094057568979266</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
@@ -10235,76 +10235,76 @@
         <v>-0</v>
       </c>
       <c r="AS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.3788541229600847</v>
+        <v>0.2073446075284663</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.02002432028703454</v>
+        <v>-0.1021382012801091</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.0537832826708846</v>
+        <v>-0.1699627784858929</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
         <v>-0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>-0</v>
       </c>
       <c r="BC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.02567039992278922</v>
+        <v>-0.008916060820183105</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-0.08722740345542909</v>
+        <v>-0.0889632209320627</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.1588901218277173</v>
+        <v>0.004892060988029257</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
         <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.09512377735409479</v>
+        <v>0.02156004691294186</v>
       </c>
       <c r="BN18" t="n">
         <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.04532458934689555</v>
+        <v>0.06863112004905807</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.1683650859671933</v>
+        <v>0.04123825148284205</v>
       </c>
       <c r="BQ18" t="n">
         <v>-0</v>
@@ -10316,52 +10316,52 @@
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.1972801687845852</v>
+        <v>0.1911095433185118</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.04557375486365192</v>
+        <v>-0.07834965102647469</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.04486630689517677</v>
+        <v>-0.00634996875851779</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.09566893117433006</v>
+        <v>-0.06230651170004931</v>
       </c>
       <c r="CF18" t="n">
         <v>-0</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.006156013003339835</v>
+        <v>0.1027376169915087</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.0003908594452586483</v>
+        <v>0.006500596481584941</v>
       </c>
       <c r="CI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ18" t="n">
         <v>0</v>
@@ -10370,76 +10370,76 @@
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.04257397896893798</v>
+        <v>-0.06589624624950027</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>-0.0514503192152873</v>
+        <v>0.117234876076921</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.1334708358238356</v>
+        <v>0.0692559473553214</v>
       </c>
       <c r="CR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.08058410697657616</v>
+        <v>-0.06090610933693862</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.02812798948082702</v>
+        <v>0.1096004166494002</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.004999455747070466</v>
+        <v>0.01858829151497193</v>
       </c>
       <c r="DA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.01589617093753493</v>
+        <v>-0.02752500733024262</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.005674847480193188</v>
+        <v>0.01765359746727394</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.01599035064372591</v>
+        <v>-0.07795722711755812</v>
       </c>
       <c r="DJ18" t="n">
         <v>-0</v>
@@ -10454,19 +10454,19 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.02765205067740414</v>
+        <v>-0.05939442257110783</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0.1636628320778024</v>
+        <v>0.03952166957986449</v>
       </c>
       <c r="DR18" t="n">
-        <v>-0.059591766250566</v>
+        <v>0.02033372575144525</v>
       </c>
       <c r="DS18" t="n">
         <v>-0</v>
@@ -10475,133 +10475,133 @@
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.07168654484259245</v>
+        <v>0.02894893304786639</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0.009180124572130374</v>
+        <v>0.01240978038716732</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.05751193517600223</v>
+        <v>-0.07810810248118902</v>
       </c>
       <c r="EB18" t="n">
         <v>0</v>
       </c>
       <c r="EC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.1159295366672388</v>
+        <v>-0.03240919137506921</v>
       </c>
       <c r="EH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.05357747010969523</v>
+        <v>0.07966362994180667</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.1084302532391055</v>
+        <v>0.03731503387029075</v>
       </c>
       <c r="EK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.05278018337554848</v>
+        <v>-0.01435360585544817</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.05786049470462667</v>
+        <v>0.06974090545780523</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.01451600057251328</v>
+        <v>-0.05833682319453071</v>
       </c>
       <c r="ET18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.07831640745346817</v>
+        <v>-0.07479035354766582</v>
       </c>
       <c r="EZ18" t="n">
         <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.01456971405688296</v>
+        <v>0.1199898345847968</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.007768096445509208</v>
+        <v>0.001314642641554766</v>
       </c>
       <c r="FC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD18" t="n">
         <v>0</v>
       </c>
       <c r="FE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF18" t="n">
         <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.0289261416623561</v>
+        <v>0.101900928645842</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>-0.08237674347544487</v>
+        <v>-0.1027180259203892</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.06977396523930299</v>
+        <v>-0.05663562548326052</v>
       </c>
       <c r="FL18" t="n">
         <v>-0</v>
@@ -10610,28 +10610,28 @@
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.00400057955062387</v>
+        <v>-0.02055055227466798</v>
       </c>
       <c r="FR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.1080351646408963</v>
+        <v>0.0746673945962564</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.008023792352087972</v>
+        <v>0.0486251076838706</v>
       </c>
       <c r="FU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV18" t="n">
         <v>0</v>
@@ -10643,31 +10643,31 @@
         <v>0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.005660237705278372</v>
+        <v>-0.009815569034051373</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>-0.06115261951224001</v>
+        <v>0.03123497253996614</v>
       </c>
       <c r="GC18" t="n">
         <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
